--- a/source/Excel/Legacy_Excel_RAW.xlsx
+++ b/source/Excel/Legacy_Excel_RAW.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ddd1d45b9ae2913d/Desktop/creditflow-data-warehouse/source/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="245" documentId="11_BB6BFAEF3CE56EECD85BAF3281E90443DD7C4B32" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDEAEC52-CC84-49DE-99DB-B9816697B978}"/>
+  <xr:revisionPtr revIDLastSave="371" documentId="11_BB6BFAEF3CE56EECD85BAF3281E90443DD7C4B32" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82231676-69FC-4565-813C-FB42566E4F1B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Loan Book 2018-2019" sheetId="1" r:id="rId1"/>
     <sheet name="Loan Book 2020-2021" sheetId="9" r:id="rId2"/>
     <sheet name="Loan Book 2022-2023" sheetId="2" r:id="rId3"/>
-    <sheet name="SF_Accounts_RAW" sheetId="3" r:id="rId4"/>
+    <sheet name="SF_Accounts" sheetId="3" r:id="rId4"/>
     <sheet name="SF_Contacts_RAW" sheetId="4" r:id="rId5"/>
     <sheet name="SF_Opportunities_RAW" sheetId="5" r:id="rId6"/>
     <sheet name="Odoo_Customers_RAW" sheetId="6" r:id="rId7"/>
@@ -27,8 +27,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Odoo_Customers_RAW!$A$1:$H$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Odoo_Invoices_RAW!$A$1:$G$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Odoo_SalesOrders_RAW!$A$1:$G$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">SF_Accounts_RAW!$C$1:$C$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">SF_Contacts_RAW!$A$1:$H$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">SF_Accounts!$D$1:$D$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">SF_Contacts_RAW!$A$1:$I$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">SF_Opportunities_RAW!$A$1:$I$77</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2823" uniqueCount="1498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2844" uniqueCount="1502">
   <si>
     <t>Loan Type</t>
   </si>
@@ -4509,6 +4509,9 @@
     <t xml:space="preserve">Company </t>
   </si>
   <si>
+    <t>Column1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Currency </t>
   </si>
   <si>
@@ -4543,16 +4546,26 @@
   </si>
   <si>
     <t>2022-2023</t>
+  </si>
+  <si>
+    <t>Phon</t>
+  </si>
+  <si>
+    <t>Account_ID2</t>
+  </si>
+  <si>
+    <t>Account_Nam</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="170" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="171" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="173" formatCode="[$-409]d\-mmm\-yyyy;@"/>
     <numFmt numFmtId="174" formatCode="#,##0.0"/>
   </numFmts>
@@ -4630,26 +4643,332 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="173" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="45">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="171" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="173" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F4E78"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -5211,51 +5530,85 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A05BBCF6-1210-4DC0-9533-B5200DAA00DB}" name="LoanBook2018_2019" displayName="LoanBook2018_2019" ref="A1:H10" totalsRowShown="0" headerRowDxfId="25" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A05BBCF6-1210-4DC0-9533-B5200DAA00DB}" name="LoanBook2018_2019" displayName="LoanBook2018_2019" ref="A1:H10" totalsRowShown="0" headerRowDxfId="41" dataDxfId="42">
   <autoFilter ref="A1:H10" xr:uid="{A05BBCF6-1210-4DC0-9533-B5200DAA00DB}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{6F4F91A1-5EB1-45DE-A0B4-823805A3C26D}" name="Company " dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{0EE21108-9482-497B-B8D7-8FB5F1856FC3}" name="Loan Type" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{F771C2BD-7186-4D2D-9A03-D1F387C31B8F}" name="Amount (PKR)" dataDxfId="5" dataCellStyle="Comma"/>
-    <tableColumn id="7" xr3:uid="{337C5E84-FD05-462F-870C-6CBFE09F976D}" name="Currency " dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{2D8521EB-3F32-4DEE-A8D2-2BCC413D4A6A}" name="Date " dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{B53ED3AC-975A-4BCB-BA90-CD5004EC954C}" name="Status " dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{43999634-8CC3-4B7A-9FD5-F1868B40D4E9}" name="Notes " dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{9463979B-50CD-4BFE-BECC-FB920026A7EC}" name="Source_Block" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{6F4F91A1-5EB1-45DE-A0B4-823805A3C26D}" name="Company " dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{0EE21108-9482-497B-B8D7-8FB5F1856FC3}" name="Loan Type" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{F771C2BD-7186-4D2D-9A03-D1F387C31B8F}" name="Amount (PKR)" dataDxfId="21" dataCellStyle="Comma"/>
+    <tableColumn id="7" xr3:uid="{337C5E84-FD05-462F-870C-6CBFE09F976D}" name="Currency " dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{2D8521EB-3F32-4DEE-A8D2-2BCC413D4A6A}" name="Date " dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{B53ED3AC-975A-4BCB-BA90-CD5004EC954C}" name="Status " dataDxfId="43"/>
+    <tableColumn id="8" xr3:uid="{43999634-8CC3-4B7A-9FD5-F1868B40D4E9}" name="Notes " dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{9463979B-50CD-4BFE-BECC-FB920026A7EC}" name="Source_Block" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D3547EAB-DFED-4FDB-88D1-2FF31D216BEA}" name="LoanBook2020_2021" displayName="LoanBook2020_2021" ref="A1:H10" totalsRowShown="0" headerRowDxfId="21" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D3547EAB-DFED-4FDB-88D1-2FF31D216BEA}" name="LoanBook2020_2021" displayName="LoanBook2020_2021" ref="A1:H10" totalsRowShown="0" headerRowDxfId="37" dataDxfId="38">
   <autoFilter ref="A1:H10" xr:uid="{D3547EAB-DFED-4FDB-88D1-2FF31D216BEA}"/>
   <tableColumns count="8">
-    <tableColumn id="2" xr3:uid="{DDF43C0F-2C20-4ECB-B696-D8C254759644}" name="Company " dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{02B472B1-A7A7-40A0-8D6C-3238854C6FCD}" name="Loan_Type " dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{DF82B8DF-AA80-439B-8924-A5B778451BEE}" name="Amount (PKR)" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{24417B60-B7A2-4BF6-A03B-93CDDCD232FF}" name="Currency " dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{6886E7D0-E9AB-47E9-8BD6-5BE7CFB8376B}" name="Date" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{FE2227F6-EFD3-4D69-B2DE-078905CE4DD8}" name="Status " dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{848C9ED1-F93B-432C-A481-114FA354AC15}" name="Notes " dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{63B72437-E05B-4B81-A728-701FE83F532D}" name="Source_Block" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{DDF43C0F-2C20-4ECB-B696-D8C254759644}" name="Company " dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{02B472B1-A7A7-40A0-8D6C-3238854C6FCD}" name="Loan_Type " dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{DF82B8DF-AA80-439B-8924-A5B778451BEE}" name="Amount (PKR)" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{24417B60-B7A2-4BF6-A03B-93CDDCD232FF}" name="Currency " dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{6886E7D0-E9AB-47E9-8BD6-5BE7CFB8376B}" name="Date" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{FE2227F6-EFD3-4D69-B2DE-078905CE4DD8}" name="Status " dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{848C9ED1-F93B-432C-A481-114FA354AC15}" name="Notes " dataDxfId="39"/>
+    <tableColumn id="10" xr3:uid="{63B72437-E05B-4B81-A728-701FE83F532D}" name="Source_Block" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{48AAD93C-FDAD-4126-8C35-A7F9362A6487}" name="LoanBook2022_2023" displayName="LoanBook2022_2023" ref="A1:H10" totalsRowShown="0" headerRowDxfId="18" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{48AAD93C-FDAD-4126-8C35-A7F9362A6487}" name="LoanBook2022_2023" displayName="LoanBook2022_2023" ref="A1:H10" totalsRowShown="0" headerRowDxfId="34" dataDxfId="35">
   <autoFilter ref="A1:H10" xr:uid="{48AAD93C-FDAD-4126-8C35-A7F9362A6487}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{AEF07859-0BBA-41BC-8AA2-9EF1BF9FA0C5}" name="Company " dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{A32039D9-A041-47C0-AFCA-BBCCBA9E4D68}" name="Loan_Type " dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{57EB1DFC-1C60-4448-AE9C-3CC21FDA9E3D}" name="Amount (PKR)" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{AEF07859-0BBA-41BC-8AA2-9EF1BF9FA0C5}" name="Company " dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{A32039D9-A041-47C0-AFCA-BBCCBA9E4D68}" name="Loan_Type " dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{57EB1DFC-1C60-4448-AE9C-3CC21FDA9E3D}" name="Amount (PKR)" dataDxfId="16"/>
     <tableColumn id="5" xr3:uid="{2E47973A-F790-4CC7-8B43-E6D976DB957A}" name="Currency "/>
-    <tableColumn id="7" xr3:uid="{0D9B54D3-BF64-4D11-AC32-AD656FCA37E6}" name="Date" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{7D8DEAF7-265A-4939-85A4-C102A9FA1AA2}" name="Status " dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{70D7F3A1-6863-4AAF-81AA-926E7A9D75F2}" name="Notes " dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{3868B4B9-DAA8-4275-89CD-7ADE7182F836}" name="Source_Block" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{0D9B54D3-BF64-4D11-AC32-AD656FCA37E6}" name="Date" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{7D8DEAF7-265A-4939-85A4-C102A9FA1AA2}" name="Status " dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{70D7F3A1-6863-4AAF-81AA-926E7A9D75F2}" name="Notes " dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{3868B4B9-DAA8-4275-89CD-7ADE7182F836}" name="Source_Block" dataDxfId="27"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A08F1A6-4CEA-4637-9187-289C1A7FA6D9}" name="Table4" displayName="Table4" ref="A1:N38" totalsRowShown="0" headerRowDxfId="7" dataDxfId="8">
+  <autoFilter ref="A1:N38" xr:uid="{6A08F1A6-4CEA-4637-9187-289C1A7FA6D9}"/>
+  <tableColumns count="14">
+    <tableColumn id="15" xr3:uid="{B043FCEB-84DD-4227-B18C-B8916CAAAEF8}" name="Account_ID" dataDxfId="1">
+      <calculatedColumnFormula>TRIM(Table4[[#This Row],[Account_ID2]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="1" xr3:uid="{FDFB0876-A47B-431B-9CE8-04201FA855BD}" name="Account_ID2" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{EE7D8474-8AE9-4A95-91FE-9D4AFB8323E6}" name="Account_Name" dataDxfId="14">
+      <calculatedColumnFormula>PROPER(TRIM(D2))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{EB310E7B-CC41-4328-A728-3D8587F0F036}" name="Column1" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{905C4B6E-6794-4497-879B-15227D44ABAD}" name="Industry" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{14952674-1DB4-4C45-9D64-1CBCA72EC08C}" name="Billing_City" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{F439CEE5-3CFF-4CE5-891F-501BF487AD00}" name="Billing_Country" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{65EF537A-5DF8-40EE-A41D-962E0307B1C4}" name="Phone" dataDxfId="0">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.clean, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(I2)," ",""),"-",""),"(",""),")",""),
+     _xlpm.converted, IF(LEFT(_xlpm.clean,3)="+92","0"&amp;MID(_xlpm.clean,4,20),
+                 IF(LEFT(_xlpm.clean,2)="92","0"&amp;MID(_xlpm.clean,3,20),
+                    _xlpm.clean)),
+     IF(TRIM(I2)="","N/A",
+        IF(LEN(_xlpm.converted)&gt;=10, _xlpm.converted, "N/A")))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{AE397EE4-03D9-4B23-B2FA-53699C63EEDF}" name="Phon" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{DCB8C944-BE8A-4452-B785-D37DC12E34DD}" name="Annual_Revenue" dataDxfId="2" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{DDAC155A-5242-4492-AAE6-E93039C15125}" name="Account_Owner" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{CE8693E3-BDB5-4DFE-BE72-9EC21E699E22}" name="Date" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{126DDED6-97FF-4C08-AC4E-C10B53B4B5D1}" name="Created_Date" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{DF088BBC-5472-4C23-9005-E1B5E66D7332}" name="Rating" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5551,7 +5904,7 @@
   <cols>
     <col min="1" max="1" width="20.140625" customWidth="1"/>
     <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="8" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" customWidth="1"/>
@@ -5566,23 +5919,23 @@
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -5592,13 +5945,13 @@
       <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="10">
         <v>10767728</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="12">
         <v>43155</v>
       </c>
       <c r="F2" s="4" t="s">
@@ -5606,7 +5959,7 @@
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -5616,13 +5969,13 @@
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="10">
         <v>6920383</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="12">
         <v>43469</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -5630,7 +5983,7 @@
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -5640,21 +5993,21 @@
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="10">
         <v>11295311</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="12">
         <v>43337</v>
       </c>
       <c r="F4" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -5664,13 +6017,13 @@
       <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="10">
         <v>5692472</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="12">
         <v>43645</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -5678,7 +6031,7 @@
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -5688,13 +6041,13 @@
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="10">
         <v>8799526</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="12">
         <v>43675</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -5702,7 +6055,7 @@
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -5712,13 +6065,13 @@
       <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="10">
         <v>4550551</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="12">
         <v>43324</v>
       </c>
       <c r="F7" s="4" t="s">
@@ -5726,23 +6079,23 @@
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="10">
         <v>708234</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="12">
         <v>43460</v>
       </c>
       <c r="F8" s="4" t="s">
@@ -5750,7 +6103,7 @@
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -5760,13 +6113,13 @@
       <c r="B9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="10">
         <v>8809604</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="12">
         <v>43164</v>
       </c>
       <c r="F9" s="4" t="s">
@@ -5774,7 +6127,7 @@
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -5784,13 +6137,13 @@
       <c r="B10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="10">
         <v>894355</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="12">
         <v>43331</v>
       </c>
       <c r="F10" s="4" t="s">
@@ -5798,7 +6151,7 @@
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -5941,41 +6294,41 @@
         <v>1485</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="13">
         <v>8035808</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="12">
         <v>44150</v>
       </c>
       <c r="F2" s="4" t="s">
@@ -5985,7 +6338,7 @@
         <v>19</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -5995,13 +6348,13 @@
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="13">
         <v>12051651</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="12">
         <v>44038</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -6011,7 +6364,7 @@
         <v>19</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -6021,20 +6374,20 @@
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="13">
         <v>1637730</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="12">
         <v>44204</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6044,13 +6397,13 @@
       <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="14">
         <v>13341868</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="12">
         <v>43980</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -6060,7 +6413,7 @@
         <v>20</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -6070,13 +6423,13 @@
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="13">
         <v>2291327</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="12">
         <v>44111</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -6086,7 +6439,7 @@
         <v>22</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -6096,13 +6449,13 @@
       <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="13">
         <v>10505272</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="12">
         <v>44104</v>
       </c>
       <c r="F7" s="4" t="s">
@@ -6112,7 +6465,7 @@
         <v>22</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -6122,13 +6475,13 @@
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="13">
         <v>2749600</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="12">
         <v>44198</v>
       </c>
       <c r="F8" s="4" t="s">
@@ -6138,7 +6491,7 @@
         <v>19</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -6148,13 +6501,13 @@
       <c r="B9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="13">
         <v>3247879</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="12">
         <v>44334</v>
       </c>
       <c r="F9" s="4" t="s">
@@ -6164,7 +6517,7 @@
         <v>22</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -6174,13 +6527,13 @@
       <c r="B10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="13">
         <v>4233840</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="12">
         <v>43846</v>
       </c>
       <c r="F10" s="4" t="s">
@@ -6190,7 +6543,7 @@
         <v>22</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
   </sheetData>
@@ -6221,25 +6574,25 @@
         <v>1485</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -6249,13 +6602,13 @@
       <c r="B2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="13">
         <v>1892247</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="12">
         <v>44882</v>
       </c>
       <c r="F2" s="4" t="s">
@@ -6263,7 +6616,7 @@
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -6273,13 +6626,13 @@
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="13">
         <v>13874508</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="12">
         <v>44813</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -6287,7 +6640,7 @@
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -6297,13 +6650,13 @@
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="13">
         <v>15348980</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="12">
         <v>44756</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -6311,7 +6664,7 @@
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6321,13 +6674,13 @@
       <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="13">
         <v>2430282</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="12">
         <v>44863</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -6335,7 +6688,7 @@
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -6345,13 +6698,13 @@
       <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="13">
         <v>5140138</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="12">
         <v>44746</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -6359,7 +6712,7 @@
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -6369,13 +6722,13 @@
       <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="13">
         <v>7375713</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="12">
         <v>45026</v>
       </c>
       <c r="F7" s="4" t="s">
@@ -6383,7 +6736,7 @@
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -6393,13 +6746,13 @@
       <c r="B8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="13">
         <v>4430739</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="12">
         <v>44688</v>
       </c>
       <c r="F8" s="4" t="s">
@@ -6407,7 +6760,7 @@
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -6417,13 +6770,13 @@
       <c r="B9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="13">
         <v>5965342</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="12">
         <v>45085</v>
       </c>
       <c r="F9" s="4" t="s">
@@ -6431,7 +6784,7 @@
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -6441,13 +6794,13 @@
       <c r="B10" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="13">
         <v>5636175</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="12">
         <v>44905</v>
       </c>
       <c r="F10" s="4" t="s">
@@ -6455,7 +6808,7 @@
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -6475,1390 +6828,1870 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" customWidth="1"/>
-    <col min="3" max="3" width="34" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="17" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="6" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="16" style="16" customWidth="1"/>
+    <col min="9" max="9" width="18.5703125" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="11" max="11" width="20" style="18" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="12.140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="3"/>
       <c r="D1" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="15" t="s">
+        <v>1499</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="17" t="s">
+        <v>1496</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01072</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="4" t="str">
-        <f>PROPER(TRIM(C2))</f>
+      <c r="C2" s="4" t="str">
+        <f>PROPER(TRIM(D2))</f>
         <v>Sunrise Textiles Mills</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="str">
+        <f t="shared" ref="H2:H38" si="0">_xlfn.LET(_xlpm.clean, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(I2)," ",""),"-",""),"(",""),")",""),
+     _xlpm.converted, IF(LEFT(_xlpm.clean,3)="+92","0"&amp;MID(_xlpm.clean,4,20),
+                 IF(LEFT(_xlpm.clean,2)="92","0"&amp;MID(_xlpm.clean,3,20),
+                    _xlpm.clean)),
+     IF(TRIM(I2)="","N/A",
+        IF(LEN(_xlpm.converted)&gt;=10, _xlpm.converted, "N/A")))</f>
+        <v>0324957885</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="8">
+      <c r="J2" s="11">
         <v>118247990</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="L2" s="12">
+        <f>IF(ISNUMBER(M2),M2,IFERROR(DATEVALUE(M2),IFERROR(DATE(VALUE(RIGHT(M2,4)),VALUE(MID(M2,4,2)),VALUE(LEFT(M2,2))),"")))</f>
+        <v>45469</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01062</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="4" t="str">
-        <f t="shared" ref="B3:B38" si="0">PROPER(TRIM(C3))</f>
+      <c r="C3" s="4" t="str">
+        <f t="shared" ref="C3:C38" si="1">PROPER(TRIM(D3))</f>
         <v>Faisal Steel Industries</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0300531003</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="8">
+      <c r="J3" s="11">
         <v>132120579</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="L3" s="12">
+        <f t="shared" ref="L3:L37" si="2">IF(ISNUMBER(M3),M3,IFERROR(DATEVALUE(M3),IFERROR(DATE(VALUE(RIGHT(M3,4)),VALUE(MID(M3,4,2)),VALUE(LEFT(M3,2))),"")))</f>
+        <v>45086</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01055</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="4" t="str">
+      <c r="C4" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Union Cotton Traders</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>Union Cotton Traders</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="4" t="s">
+        <v>0283487347</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="11">
+        <v>244720065</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" s="12">
+        <f t="shared" si="2"/>
+        <v>44874</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01036</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Lahore Auto Parts Ltd</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>03280164005</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="11">
+        <v>194426163</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" s="12">
+        <f t="shared" si="2"/>
+        <v>45679</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01007</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Crescent Steel Works</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0289593103</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" s="11">
+        <v>79617971</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L6" s="12">
+        <f t="shared" si="2"/>
+        <v>45289</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01031</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Al-Rehman Rice Mills</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>03134751079</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J7" s="11">
+        <v>76189194</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" s="12">
+        <f t="shared" si="2"/>
+        <v>45318</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01044</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Highland Tea Traders</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>N/A</v>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="J8" s="11">
+        <v>93637396</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" s="12">
+        <f t="shared" si="2"/>
+        <v>45600</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01061</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Ravi River Mills</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0310162720</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="J9" s="11">
+        <v>95597113</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="12">
+        <f t="shared" si="2"/>
+        <v>45078</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01069</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Bright Future Foods</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0484987769</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="J10" s="11">
+        <v>241661069</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L10" s="12">
+        <f t="shared" si="2"/>
+        <v>45338</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01023</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Sunrise Textiles Mills</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0317010651</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="J11" s="11">
+        <v>118247990</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="12">
+        <f t="shared" si="2"/>
+        <v>45469</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01065</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Apex Consulting Grp</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0331241904</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="J12" s="11">
+        <v>25400148</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="12">
+        <f t="shared" si="2"/>
+        <v>45179</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01043</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Green Fields Agriculture</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="8">
-        <v>244720065</v>
-      </c>
-      <c r="I4" s="4" t="s">
+      <c r="H13" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0304586850</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="J13" s="11">
+        <v>34099087</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L13" s="12">
+        <f t="shared" si="2"/>
+        <v>45455</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01066</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Northern Textiles Ventures</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>N/A</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J14" s="11">
+        <v>136587518</v>
+      </c>
+      <c r="K14" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K4" s="4" t="s">
+      <c r="L14" s="12">
+        <f t="shared" si="2"/>
+        <v>44875</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="N14" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="4" t="str">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01056</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Delta Chemical Industries</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>Lahore Auto Parts Ltd</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="4" t="s">
+        <v>N/A</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J15" s="11">
+        <v>241399474</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L15" s="12">
+        <f t="shared" si="2"/>
+        <v>45173</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01030</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Indus Valley Agro</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>03423619399</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="J16" s="11">
+        <v>156726947</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L16" s="12">
+        <f t="shared" si="2"/>
+        <v>45050</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01010</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Blue Ocean Logistics Ltd</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>03441928327</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="J17" s="11">
+        <v>63952498</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="12">
+        <f t="shared" si="2"/>
+        <v>45031</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01033</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Karachi Electronics Co</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>N/A</v>
+      </c>
+      <c r="I18" s="9"/>
+      <c r="J18" s="11">
+        <v>153504841</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L18" s="12">
+        <f t="shared" si="2"/>
+        <v>44978</v>
+      </c>
+      <c r="M18" s="5">
+        <v>44978</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01051</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Millennium Plastics Ltd</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0331769367</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="J19" s="11">
+        <v>244621546</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L19" s="12">
+        <f t="shared" si="2"/>
+        <v>45010</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01059</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Everest Trading Co</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" s="4" t="str">
+        <f>_xlfn.LET(_xlpm.clean, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(I20)," ",""),"-",""),"(",""),")",""),
+     _xlpm.converted, IF(LEFT(_xlpm.clean,3)="+92","0"&amp;MID(_xlpm.clean,4,20),
+                 IF(LEFT(_xlpm.clean,2)="92","0"&amp;MID(_xlpm.clean,3,20),
+                    _xlpm.clean)),
+     IF(TRIM(I20)="","N/A",
+        IF(LEN(_xlpm.converted)&gt;=10, _xlpm.converted, "N/A")))</f>
+        <v>N/A</v>
+      </c>
+      <c r="I20" s="9"/>
+      <c r="J20" s="11">
+        <v>219249699</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L20" s="12">
+        <f t="shared" si="2"/>
+        <v>45836</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01053</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Skyline Real Estate Developers</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>03283172788</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="J21" s="11">
+        <v>223776643</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L21" s="12">
+        <f t="shared" si="2"/>
+        <v>45329</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01046</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Metro Pharma Distributors</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>N/A</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J22" s="11">
+        <v>5108968</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L22" s="12">
+        <f t="shared" si="2"/>
+        <v>45804</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01006</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Zenith Apparel Mfg.</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H23" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0230265423</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J23" s="11">
+        <v>232497537</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L23" s="12">
+        <f t="shared" si="2"/>
+        <v>45660</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01020</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Horizon Pharmaceuticals</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H24" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0288346578</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J24" s="11">
+        <v>10646341</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="12">
+        <f t="shared" si="2"/>
+        <v>44707</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01012</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C25" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Prime Motors Ltd</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F25" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G25" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="8">
-        <v>194426163</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="H25" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>03473953767</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="J25" s="11">
+        <v>149680614</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L25" s="12">
+        <f t="shared" si="2"/>
+        <v>45627</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01073</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Falcon Foods Processing.</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0274431351</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="J26" s="11">
+        <v>153505445</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="12">
+        <f t="shared" si="2"/>
+        <v>45661</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01048</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Al Fateh Engineering</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0323872148</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="J27" s="11">
+        <v>185602212</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="12">
+        <f t="shared" si="2"/>
+        <v>44685</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01003</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C28" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Al Habib Textiles Pvt Ltd</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0334332181</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="J28" s="11">
+        <v>67454433</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L28" s="12">
+        <f t="shared" si="2"/>
+        <v>45540</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01021</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Metro Retail Group</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H29" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>03360518347</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="J29" s="11">
+        <v>131881663</v>
+      </c>
+      <c r="K29" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5" s="4" t="s">
+      <c r="L29" s="12">
+        <f t="shared" si="2"/>
+        <v>44755</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01015</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C30" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Falcon Foods Processing</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H30" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0400122691</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="J30" s="11">
+        <v>153505445</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="12">
+        <f t="shared" si="2"/>
+        <v>45661</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="N30" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="4" t="str">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01024</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Pearl Continental Exports</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H31" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>Crescent Steel Works</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
+        <v>0318013267</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="J31" s="11">
+        <v>106729822</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L31" s="12">
+        <f t="shared" si="2"/>
+        <v>45146</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01018</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C32" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>National Grain Traders</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>03485430391</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="J32" s="11">
+        <v>210577115</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L32" s="12">
+        <f t="shared" si="2"/>
+        <v>45104</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01071</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C33" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Everest Trading Co</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>N/A</v>
+      </c>
+      <c r="I33" s="9"/>
+      <c r="J33" s="11">
+        <v>219249699</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L33" s="12">
+        <f t="shared" si="2"/>
+        <v>45836</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01027</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Gulf Star Trading Co</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G34" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H6" s="8">
-        <v>79617971</v>
-      </c>
-      <c r="I6" s="4" t="s">
+      <c r="H34" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0222343098</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="J34" s="11">
+        <v>139982870</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L34" s="12">
+        <f t="shared" si="2"/>
+        <v>44726</v>
+      </c>
+      <c r="M34" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01016</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C35" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Silver Line Construction Co.</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H35" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>03322704828</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="J35" s="11">
+        <v>58394792</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L35" s="12">
+        <f t="shared" si="2"/>
+        <v>44563</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01041</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C36" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Coastal Shipping Services</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H36" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0285634216</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="J36" s="11">
+        <v>86924049</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="12">
+        <f t="shared" si="2"/>
+        <v>44957</v>
+      </c>
+      <c r="M36" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01070</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C37" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Karachi Electronics Co.</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H37" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0343545494</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="J37" s="11">
+        <v>153504841</v>
+      </c>
+      <c r="K37" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="K6" s="4" t="s">
+      <c r="L37" s="12">
+        <f t="shared" si="2"/>
+        <v>44978</v>
+      </c>
+      <c r="M37" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="N37" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="4" t="str">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="str">
+        <f>TRIM(Table4[[#This Row],[Account_ID2]])</f>
+        <v>SF-01039</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C38" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Punjab Dairy Farms</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H38" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>Al-Rehman Rice Mills</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H7" s="8">
-        <v>76189194</v>
-      </c>
-      <c r="I7" s="4" t="s">
+        <v>N/A</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J38" s="11">
+        <v>155292587</v>
+      </c>
+      <c r="K38" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="J7" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="K7" s="4" t="s">
+      <c r="L38" s="12">
+        <f>IF(ISNUMBER(M38),M38,IFERROR(DATEVALUE(M38),IFERROR(DATE(VALUE(RIGHT(M38,4)),VALUE(MID(M38,4,2)),VALUE(LEFT(M38,2))),"")))</f>
+        <v>45046</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="N38" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B8" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Highland Tea Traders</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="8">
-        <v>93637396</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Ravi River Mills</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="8">
-        <v>95597113</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Bright Future Foods</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="H10" s="8">
-        <v>241661069</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Sunrise Textiles Mills</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="H11" s="8">
-        <v>118247990</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B12" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Apex Consulting Grp</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="H12" s="8">
-        <v>25400148</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="K12" s="4"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Green Fields Agriculture</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="H13" s="8">
-        <v>34099087</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="K13" s="4"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B14" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Northern Textiles Ventures</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="H14" s="8">
-        <v>136587518</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B15" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Delta Chemical Industries</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="H15" s="8">
-        <v>241399474</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B16" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Indus Valley Agro</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="H16" s="8">
-        <v>156726947</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B17" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Blue Ocean Logistics Ltd</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="H17" s="8">
-        <v>63952498</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B18" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Karachi Electronics Co</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="8">
-        <v>153504841</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B19" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Millennium Plastics Ltd</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="H19" s="8">
-        <v>244621546</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="K19" s="4"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B20" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Everest Trading Co</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="8">
-        <v>219249699</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B21" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Skyline Real Estate Developers</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="H21" s="8">
-        <v>223776643</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B22" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Metro Pharma Distributors</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="H22" s="8">
-        <v>5108968</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B23" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Zenith Apparel Mfg.</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="H23" s="8">
-        <v>232497537</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B24" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Horizon Pharmaceuticals</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H24" s="8">
-        <v>10646341</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B25" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Prime Motors Ltd</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="H25" s="8">
-        <v>149680614</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Falcon Foods Processing.</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="H26" s="8">
-        <v>153505445</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B27" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Al Fateh Engineering</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H27" s="8">
-        <v>185602212</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Al Habib Textiles Pvt Ltd</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="H28" s="8">
-        <v>67454433</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Metro Retail Group</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="H29" s="8">
-        <v>131881663</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Falcon Foods Processing</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H30" s="8">
-        <v>153505445</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B31" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Pearl Continental Exports</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="H31" s="8">
-        <v>106729822</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="K31" s="4"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>National Grain Traders</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="H32" s="8">
-        <v>210577115</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="K32" s="4"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B33" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Everest Trading Co</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="8">
-        <v>219249699</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B34" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Gulf Star Trading Co</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H34" s="8">
-        <v>139982870</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B35" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Silver Line Construction Co.</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="H35" s="8">
-        <v>58394792</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B36" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Coastal Shipping Services</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="H36" s="8">
-        <v>86924049</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B37" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Karachi Electronics Co.</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="H37" s="8">
-        <v>153504841</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="K37" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B38" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Punjab Dairy Farms</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="H38" s="8">
-        <v>155292587</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="C1:C38" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="32" customWidth="1"/>
-    <col min="7" max="8" width="16" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>211</v>
       </c>
@@ -7866,1164 +8699,1577 @@
         <v>34</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="4" t="str">
+        <f>PROPER(TRIM(C2))</f>
+        <v>Sunrise Textiles Mills</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J2" t="str">
+        <f>_xlfn.LET(
+    _xlpm.PrimaryNum, IF(OR(H2="", H2="N/A"), I2, H2),
+    _xlpm.Clean1, SUBSTITUTE(_xlpm.PrimaryNum, "-", ""),
+    _xlpm.Clean2, SUBSTITUTE(_xlpm.Clean1, " ", ""),
+    _xlpm.Clean3, SUBSTITUTE(_xlpm.Clean2, "+", ""),
+    _xlpm.Clean4, SUBSTITUTE(_xlpm.Clean3, "(", ""),
+    _xlpm.Clean5, SUBSTITUTE(_xlpm.Clean4, ")", ""),
+    _xlpm.Format92, IF(LEFT(_xlpm.Clean5, 2)="92", "0" &amp; MID(_xlpm.Clean5, 3, LEN(_xlpm.Clean5)), _xlpm.Clean5),
+    IF(LEN(_xlpm.Format92)&gt;=10, _xlpm.Format92, "N/A")
+)</f>
+        <v>0371318699</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="4" t="str">
+        <f t="shared" ref="B3:B47" si="0">PROPER(TRIM(C3))</f>
+        <v>Faisal Steel Industries</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J47" si="1">_xlfn.LET(
+    _xlpm.PrimaryNum, IF(OR(H3="", H3="N/A"), I3, H3),
+    _xlpm.Clean1, SUBSTITUTE(_xlpm.PrimaryNum, "-", ""),
+    _xlpm.Clean2, SUBSTITUTE(_xlpm.Clean1, " ", ""),
+    _xlpm.Clean3, SUBSTITUTE(_xlpm.Clean2, "+", ""),
+    _xlpm.Clean4, SUBSTITUTE(_xlpm.Clean3, "(", ""),
+    _xlpm.Clean5, SUBSTITUTE(_xlpm.Clean4, ")", ""),
+    _xlpm.Format92, IF(LEFT(_xlpm.Clean5, 2)="92", "0" &amp; MID(_xlpm.Clean5, 3, LEN(_xlpm.Clean5)), _xlpm.Clean5),
+    IF(LEN(_xlpm.Format92)&gt;=10, _xlpm.Format92, "N/A")
+)</f>
+        <v>0287134936</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Union Cotton Traders</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" s="4"/>
+      <c r="J4" t="str">
+        <f t="shared" si="1"/>
+        <v>0347174648</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Lahore Auto Parts Ltd</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J5" t="str">
+        <f t="shared" si="1"/>
+        <v>0429671756</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Crescent Steel Works</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J6" t="str">
+        <f t="shared" si="1"/>
+        <v>0327703482</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Al-Rehman Rice Mills</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" s="4"/>
+      <c r="J7" t="str">
+        <f t="shared" si="1"/>
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Highland Tea Traders</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J8" t="str">
+        <f t="shared" si="1"/>
+        <v>0316753396</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Ravi River Mills</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>231</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>231</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="G9" s="4"/>
       <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" s="4"/>
+      <c r="J9" t="str">
+        <f t="shared" si="1"/>
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Ravi River Mills</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="I10" s="4" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J10" t="str">
+        <f t="shared" si="1"/>
+        <v>0330455623</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Bright Future Foods</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="I11" s="4" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J11" t="str">
+        <f t="shared" si="1"/>
+        <v>0335946474</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunrise Textiles Mills</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E12" s="4"/>
       <c r="F12" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="I12" s="4" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J12" t="str">
+        <f t="shared" si="1"/>
+        <v>03025339421</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunrise Textiles Mills</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="E13" s="4"/>
       <c r="F13" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="H13" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="I13" s="4" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J13" t="str">
+        <f t="shared" si="1"/>
+        <v>0345171236</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Apex Consulting Grp</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="I14" s="4" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J14" t="str">
+        <f t="shared" si="1"/>
+        <v>0304612004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Green Fields Agriculture</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="H15" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="I15" s="4" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J15" t="str">
+        <f t="shared" si="1"/>
+        <v>0311585064</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Northern Textiles Ventures</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="H16" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="I16" s="4" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J16" t="str">
+        <f t="shared" si="1"/>
+        <v>03152284210</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Delta Chemical Industries</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4" t="s">
+      <c r="F17" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="I17" s="4" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J17" t="str">
+        <f t="shared" si="1"/>
+        <v>0338470076</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Indus Valley Agro</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="H18" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" s="4"/>
+      <c r="J18" t="str">
+        <f t="shared" si="1"/>
+        <v>0348367365</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Indus Valley Agro</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="I19" s="4" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J19" t="str">
+        <f t="shared" si="1"/>
+        <v>0321656049</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Blue Ocean Logistics Ltd</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="H20" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="I20" s="4" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J20" t="str">
+        <f t="shared" si="1"/>
+        <v>0305502296</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Blue Ocean Logistics Ltd</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="4"/>
+      <c r="H21" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="I21" s="4" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J21" t="str">
+        <f t="shared" si="1"/>
+        <v>0454767976</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Karachi Electronics Co</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="E22" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="F22" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="G22" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="H22" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="I22" s="4" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J22" t="str">
+        <f t="shared" si="1"/>
+        <v>0346226838</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Millennium Plastics Ltd</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="E23" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E23" s="4"/>
       <c r="F23" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="4"/>
+      <c r="I23" s="4" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J23" t="str">
+        <f t="shared" si="1"/>
+        <v>0275352181</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Everest Trading Co</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="F24" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="G24" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="H24" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="I24" s="4" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J24" t="str">
+        <f t="shared" si="1"/>
+        <v>0311277997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Skyline Real Estate Developers</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+      <c r="F25" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>114</v>
+      </c>
       <c r="H25" s="4"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I25" s="4"/>
+      <c r="J25" t="str">
+        <f t="shared" si="1"/>
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Metro Pharma Distributors</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="F26" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="H26" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="H26" s="4"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I26" s="4"/>
+      <c r="J26" t="str">
+        <f t="shared" si="1"/>
+        <v>0462554665</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Zenith Apparel Mfg.</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="E27" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="F27" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="H27" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="I27" s="4" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J27" t="str">
+        <f t="shared" si="1"/>
+        <v>0328652816</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Horizon Pharmaceuticals</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="E28" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="G28" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="H28" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="I28" s="4" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J28" t="str">
+        <f t="shared" si="1"/>
+        <v>0357383473</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Horizon Pharmaceuticals</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E29" s="4"/>
       <c r="F29" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="H29" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="I29" s="4" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J29" t="str">
+        <f t="shared" si="1"/>
+        <v>0309240758</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Prime Motors Ltd</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="E30" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="F30" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="H30" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="I30" s="4" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J30" t="str">
+        <f t="shared" si="1"/>
+        <v>03467790104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Falcon Foods Processing.</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="F31" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="F31" s="4"/>
       <c r="G31" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="H31" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="I31" s="4" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J31" t="str">
+        <f t="shared" si="1"/>
+        <v>0349711798</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Falcon Foods Processing.</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="D32" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="E32" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="F32" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="G32" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="H32" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="I32" s="4" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J32" t="str">
+        <f t="shared" si="1"/>
+        <v>0320670654</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Al Fateh Engineering</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="D33" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="E33" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="F33" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="G33" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="H33" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="H33" s="4"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="4"/>
+      <c r="J33" t="str">
+        <f t="shared" si="1"/>
+        <v>0474303054</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Al Fateh Engineering</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="D34" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E34" s="4"/>
       <c r="F34" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="H34" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="I34" s="4" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J34" t="str">
+        <f t="shared" si="1"/>
+        <v>0318416169</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Al Habib Textiles Pvt Ltd</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="E35" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="F35" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="G35" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="H35" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="I35" s="4" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J35" t="str">
+        <f t="shared" si="1"/>
+        <v>0452029702</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Metro Retail Group</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="D36" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="E36" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="F36" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="G36" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="G36" s="4"/>
       <c r="H36" s="4"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I36" s="4"/>
+      <c r="J36" t="str">
+        <f t="shared" si="1"/>
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Metro Retail Group</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="D37" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="E37" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="F37" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="G37" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="H37" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="I37" s="4" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J37" t="str">
+        <f t="shared" si="1"/>
+        <v>03352583132</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Falcon Foods Processing</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="D38" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="E38" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="F38" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="G38" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="H38" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="I38" s="4" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J38" t="str">
+        <f t="shared" si="1"/>
+        <v>0511824225</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Pearl Continental Exports</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="D39" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="E39" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="F39" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="G39" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="H39" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="H39" s="4"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I39" s="4"/>
+      <c r="J39" t="str">
+        <f t="shared" si="1"/>
+        <v>0341829922</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>National Grain Traders</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="D40" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="E40" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="F40" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="G40" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="H40" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="I40" s="4" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J40" t="str">
+        <f t="shared" si="1"/>
+        <v>0317102767</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>National Grain Traders</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="D41" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="E41" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E41" s="4"/>
       <c r="F41" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="H41" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="H41" s="4" t="s">
+      <c r="I41" s="4" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J41" t="str">
+        <f t="shared" si="1"/>
+        <v>0379632595</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Everest Trading Co</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="D42" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="E42" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="F42" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="G42" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="H42" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="H42" s="4" t="s">
+      <c r="I42" s="4" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J42" t="str">
+        <f t="shared" si="1"/>
+        <v>03232456506</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Gulf Star Trading Co</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="D43" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="F43" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="H43" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="I43" s="4" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J43" t="str">
+        <f t="shared" si="1"/>
+        <v>0310002578</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Silver Line Construction Co.</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="D44" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="E44" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="F44" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="H44" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="I44" s="4" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J44" t="str">
+        <f t="shared" si="1"/>
+        <v>0229409749</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Coastal Shipping Services</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="D45" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="E45" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="F45" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="G45" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="H45" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H45" s="4" t="s">
+      <c r="I45" s="4" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J45" t="str">
+        <f t="shared" si="1"/>
+        <v>0510283857</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Karachi Electronics Co.</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="D46" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="E46" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E46" s="4"/>
       <c r="F46" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G46" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4" t="s">
+      <c r="H46" s="4"/>
+      <c r="I46" s="4" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J46" t="str">
+        <f t="shared" si="1"/>
+        <v>0501574733</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Punjab Dairy Farms</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="D47" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="E47" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="F47" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="G47" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="H47" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="I47" s="4" t="s">
         <v>404</v>
       </c>
+      <c r="J47" t="str">
+        <f t="shared" si="1"/>
+        <v>0313301657</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H47" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:I47" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
